--- a/config/Tax_Rates_2026.xlsx
+++ b/config/Tax_Rates_2026.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -579,6 +579,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -938,6 +939,106 @@
       <c r="D20" s="7" t="inlineStr">
         <is>
           <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>part_iv_tax_rate</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>0.383333333333</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>ITA s.186(1) — Part IV tax 38 1/3% of portfolio dividends; connected-corp dividends taxed only to the extent of the payer's dividend refund. CRA T4012 Ch.6 (Schedule 3).</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>capital_gains_inclusion_rate</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>ITA s.38(a) — one-half inclusion. Proposed 2/3 increase cancelled by the federal government 2025-03-21 (canada.ca, Dept. of Finance / CRA tax tip 'Update on CRA administration of the proposed capital gains taxation changes').</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>grip_general_rate_factor</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>ITA s.89(1) 'general rate factor' — 0.72 for taxation years after 2013. CRA T2 Schedule 53, Part 1 (line 150 x 0.72).</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>part_iii_1_rate</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>ITA s.185.1(1)(a) — Part III.1 tax 20% of an excessive eligible dividend designation (additional 10% under s.185.1(1)(b) if the anti-avoidance rule applies — not modelled). CRA T2 Schedule 55.</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>part_iii_rate</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>ITA s.184(2) — Part III tax 60% of the excess of a capital dividend election over the CDA; s.184(3) election can treat the excess as a separate taxable dividend. CRA Income Tax Folio S3-F2-C1.</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
